--- a/artfynd/A 14805-2023 artfynd.xlsx
+++ b/artfynd/A 14805-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1195,6 +1195,264 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>108523059</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97402</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Änghagen, 250 m VNV om, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>313102</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6458074</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Orust</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Myckleby</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>OB-Oru-0003</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spridda grupper och enstaka bladrosetter i olika riktningar</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Olle Molander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Olle Molander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>108523086</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97402</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Änghagen, 250 m NNV om, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>313243</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6458253</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Orust</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Myckleby</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>OB-Oru-0004</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spridda grupper och enstaka bladrosetter i olika riktningar</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Olle Molander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Olle Molander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14805-2023 artfynd.xlsx
+++ b/artfynd/A 14805-2023 artfynd.xlsx
@@ -1197,7 +1197,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>108523059</v>
+        <v>108523086</v>
       </c>
       <c r="B6" t="n">
         <v>97402</v>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>285</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1245,14 +1245,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Änghagen, 250 m VNV om, Boh</t>
+          <t>Änghagen, 250 m NNV om, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>313102</v>
+        <v>313243</v>
       </c>
       <c r="R6" t="n">
-        <v>6458074</v>
+        <v>6458253</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>OB-Oru-0003</t>
+          <t>OB-Oru-0004</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1326,7 +1326,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>108523086</v>
+        <v>108523059</v>
       </c>
       <c r="B7" t="n">
         <v>97402</v>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1374,14 +1374,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Änghagen, 250 m NNV om, Boh</t>
+          <t>Änghagen, 250 m VNV om, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>313243</v>
+        <v>313102</v>
       </c>
       <c r="R7" t="n">
-        <v>6458253</v>
+        <v>6458074</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>OB-Oru-0004</t>
+          <t>OB-Oru-0003</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">

--- a/artfynd/A 14805-2023 artfynd.xlsx
+++ b/artfynd/A 14805-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14805-2023 artfynd.xlsx
+++ b/artfynd/A 14805-2023 artfynd.xlsx
@@ -1180,7 +1180,7 @@
         <v>118805157</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 14805-2023 artfynd.xlsx
+++ b/artfynd/A 14805-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1309,6 +1309,125 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129914898</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97863</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Änghagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>313208</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6458135</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Orust</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Myckleby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Peter Carlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Peter Carlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14805-2023 artfynd.xlsx
+++ b/artfynd/A 14805-2023 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>129914898</v>
       </c>
       <c r="B7" t="n">
-        <v>97863</v>
+        <v>97867</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14805-2023 artfynd.xlsx
+++ b/artfynd/A 14805-2023 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>129914898</v>
       </c>
       <c r="B7" t="n">
-        <v>97867</v>
+        <v>97871</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14805-2023 artfynd.xlsx
+++ b/artfynd/A 14805-2023 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>129914898</v>
       </c>
       <c r="B7" t="n">
-        <v>97871</v>
+        <v>97874</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14805-2023 artfynd.xlsx
+++ b/artfynd/A 14805-2023 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>129914898</v>
       </c>
       <c r="B7" t="n">
-        <v>97874</v>
+        <v>97875</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14805-2023 artfynd.xlsx
+++ b/artfynd/A 14805-2023 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>129914898</v>
       </c>
       <c r="B7" t="n">
-        <v>97875</v>
+        <v>97892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14805-2023 artfynd.xlsx
+++ b/artfynd/A 14805-2023 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>129914898</v>
       </c>
       <c r="B7" t="n">
-        <v>97908</v>
+        <v>97910</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14805-2023 artfynd.xlsx
+++ b/artfynd/A 14805-2023 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>129914898</v>
       </c>
       <c r="B7" t="n">
-        <v>97910</v>
+        <v>97997</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14805-2023 artfynd.xlsx
+++ b/artfynd/A 14805-2023 artfynd.xlsx
@@ -675,65 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108523086</v>
+        <v>110649559</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2389</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Hook.) Gray</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Änghagen, 250 m NNV om, Boh</t>
+          <t>Änghagen, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>313243</v>
+        <v>313158</v>
       </c>
       <c r="R2" t="n">
-        <v>6458253</v>
+        <v>6458116</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,24 +742,19 @@
           <t>Myckleby</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>OB-Oru-0004</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spridda grupper och enstaka bladrosetter i olika riktningar</t>
+          <t>På murken låga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,78 +770,67 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Olle Molander</t>
+          <t>Peter Carlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Molander</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Peter Carlsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108523059</v>
+        <v>110513492</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Änghagen, 250 m VNV om, Boh</t>
+          <t>Änghagen, Myckleby, Orust, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>313102</v>
+        <v>313149</v>
       </c>
       <c r="R3" t="n">
-        <v>6458075</v>
+        <v>6458095</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -884,24 +855,24 @@
           <t>Myckleby</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>OB-Oru-0003</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-07-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spridda grupper och enstaka bladrosetter i olika riktningar</t>
+          <t>2023-07-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,86 +881,78 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Olle Molander</t>
+          <t>Peter Carlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Molander</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Peter Carlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110513492</v>
+        <v>129914898</v>
       </c>
       <c r="B4" t="n">
-        <v>56635</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>220686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Änghagen (Myckleby, Orust), Boh</t>
+          <t>Änghagen, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>313149.7505813161</v>
+        <v>313208</v>
       </c>
       <c r="R4" t="n">
-        <v>6458094.697411327</v>
+        <v>6458135</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,22 +976,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,57 +1018,60 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110649559</v>
+        <v>108523059</v>
       </c>
       <c r="B5" t="n">
-        <v>95200</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2389</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Änghagen, Boh</t>
+          <t>Änghagen, 250 m VNV om, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>313158.6798018678</v>
+        <v>313102</v>
       </c>
       <c r="R5" t="n">
-        <v>6458115.902556879</v>
+        <v>6458075</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1127,29 +1093,24 @@
           <t>Myckleby</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>OB-Oru-0003</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På murken låga</t>
+          <t>Spridda grupper och enstaka bladrosetter i olika riktningar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,27 +1126,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Peter Carlsson</t>
+          <t>Olle Molander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Peter Carlsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Olle Molander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118805157</v>
+        <v>108523086</v>
       </c>
       <c r="B6" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,34 +1172,30 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>285</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>6458247, 313236, Boh</t>
+          <t>Änghagen, 250 m NNV om, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>313236</v>
+        <v>313243</v>
       </c>
       <c r="R6" t="n">
-        <v>6458247</v>
+        <v>6458253</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1261,29 +1217,24 @@
           <t>Myckleby</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>OB-Oru-0004</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ca tio rosetter inom en kvadratmeter varav en blommande</t>
+          <t>Spridda grupper och enstaka bladrosetter i olika riktningar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1299,49 +1250,53 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Peter Carlsson</t>
+          <t>Olle Molander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peter Carlsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Olle Molander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129914898</v>
+        <v>118805157</v>
       </c>
       <c r="B7" t="n">
-        <v>97997</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220686</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1349,22 +1304,26 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Änghagen, Boh</t>
+          <t>6458247, 313236, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>313208</v>
+        <v>313236</v>
       </c>
       <c r="R7" t="n">
-        <v>6458135</v>
+        <v>6458247</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1388,22 +1347,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ca tio rosetter inom en kvadratmeter varav en blommande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1412,6 +1376,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14805-2023 artfynd.xlsx
+++ b/artfynd/A 14805-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110649559</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110513492</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129914898</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1139,6 +1159,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108523059</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1263,6 +1288,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108523086</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1392,8 +1422,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118805157</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>